--- a/从零开始学Slots/从零开始学Slots-11-数值篇-Scatter(3).xlsx
+++ b/从零开始学Slots/从零开始学Slots-11-数值篇-Scatter(3).xlsx
@@ -7804,6 +7804,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:K145" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8650,5 +8653,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:O95" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-11-数值篇-Scatter(3).xlsx
+++ b/从零开始学Slots/从零开始学Slots-11-数值篇-Scatter(3).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="184">
   <si>
     <r>
       <rPr>
@@ -6835,7 +6835,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6954,6 +6954,14 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -8304,8 +8312,8 @@
       <c r="H48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>145</v>
+      <c r="A49" s="30">
+        <v>3</v>
       </c>
       <c r="B49" s="18" t="n">
         <f aca="false">B40*B40*B40</f>
@@ -8555,8 +8563,8 @@
         <f aca="false">IF(B43=9,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C70" s="14" t="s">
-        <v>176</v>
+      <c r="C70" s="31">
+        <v>10</v>
       </c>
       <c r="D70" s="14"/>
       <c r="E70" s="14"/>
@@ -8590,8 +8598,8 @@
       <c r="D72" s="15"/>
     </row>
     <row r="73" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="17" t="s">
-        <v>181</v>
+      <c r="A73" s="30">
+        <v>1</v>
       </c>
       <c r="B73" s="25" t="str">
         <f aca="false">IF(B40=4,"✓","✗")</f>

--- a/从零开始学Slots/从零开始学Slots-11-数值篇-Scatter(3).xlsx
+++ b/从零开始学Slots/从零开始学Slots-11-数值篇-Scatter(3).xlsx
@@ -6654,11 +6654,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -6835,7 +6836,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6961,6 +6962,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8365,7 +8370,7 @@
       <c r="A53" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B53" s="22" t="n">
+      <c r="B53" s="32" t="n">
         <f aca="false">B52/B42^3</f>
         <v>144</v>
       </c>
@@ -8427,7 +8432,7 @@
       <c r="A59" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="22" t="n">
+      <c r="B59" s="32" t="n">
         <f aca="false">B53</f>
         <v>144</v>
       </c>
